--- a/public/assets/templates/Template_Transaksi.xlsx
+++ b/public/assets/templates/Template_Transaksi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_KULIAH\semester2\PBL\Template_Import_SIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999EEB9C-1681-49F4-AC42-EF9716FC5AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77D7C51-94CE-417F-B2BF-95FF60511DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Daftar Akun" sheetId="3" r:id="rId3"/>
     <sheet name="Daftar Kegiatan" sheetId="4" r:id="rId4"/>
     <sheet name="Sumber Anggaran" sheetId="5" r:id="rId5"/>
+    <sheet name="Unit Divisi" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="1234">
   <si>
     <t>Tanggal</t>
   </si>
@@ -3660,9 +3661,6 @@
     <t xml:space="preserve">05.08.020 | PENINGKATAN MUTU PRAKTIK IBADAH  </t>
   </si>
   <si>
-    <t>Tes</t>
-  </si>
-  <si>
     <t>Yayasan</t>
   </si>
   <si>
@@ -3670,13 +3668,89 @@
   </si>
   <si>
     <t xml:space="preserve">5-2100 | Beban administrasi Bank  </t>
+  </si>
+  <si>
+    <t>Kode Unit</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>TPA</t>
+  </si>
+  <si>
+    <t>PGRA</t>
+  </si>
+  <si>
+    <t>SDIT1</t>
+  </si>
+  <si>
+    <t>SDIT2</t>
+  </si>
+  <si>
+    <t>SMPIT</t>
+  </si>
+  <si>
+    <t>SMKIT</t>
+  </si>
+  <si>
+    <t>ASMA</t>
+  </si>
+  <si>
+    <t>SMAIT</t>
+  </si>
+  <si>
+    <t>Kurikulum</t>
+  </si>
+  <si>
+    <t>Kesiswaan</t>
+  </si>
+  <si>
+    <t>Qur'an</t>
+  </si>
+  <si>
+    <t>Tidak Terikat</t>
+  </si>
+  <si>
+    <t>dd-mm-yyyy</t>
+  </si>
+  <si>
+    <t>Judul Transaksi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3704,8 +3778,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3715,6 +3795,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3743,11 +3829,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3768,9 +3855,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C717CAF4-4DEA-491C-BE7C-66A89DF27A08}"/>
   </cellStyles>
@@ -4075,18 +4165,18 @@
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="39.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="26.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4128,39 +4218,54 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1207</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>933</v>
-      </c>
-      <c r="G2" t="s">
-        <v>865</v>
-      </c>
-      <c r="J2" t="s">
-        <v>813</v>
-      </c>
-      <c r="K2" t="s">
-        <v>865</v>
-      </c>
-      <c r="L2">
-        <v>1000000</v>
+      <c r="A2" s="8" t="s">
+        <v>1232</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{957A1D48-4DF2-45CF-AD53-E88E6F802EE9}">
+          <x14:formula1>
+            <xm:f>'Daftar Akun'!$D$1:$D$124</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E85CB116-E30C-4B0F-BC9A-AC50A92DCB5D}">
+          <x14:formula1>
+            <xm:f>'Daftar Kegiatan'!$D$1:$D$274</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{28E651D1-E48E-40C5-8110-EAD5F118D4BD}">
+          <x14:formula1>
+            <xm:f>'Sumber Anggaran'!$A$1:$A$21</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00F009F5-9B3B-4457-8F66-B1FEE9CE3F5A}">
+          <x14:formula1>
+            <xm:f>'Unit Divisi'!$B$2:$B$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{045686A4-935E-42CA-B9C9-93462483502D}">
+          <x14:formula1>
+            <xm:f>'Unit Divisi'!$D$2:$D$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{78424B41-F336-4D95-A27D-6719FB0C9C51}">
+          <x14:formula1>
+            <xm:f>'Unit Divisi'!$F$2:$F$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -4169,20 +4274,21 @@
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="39.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="26.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4221,39 +4327,81 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>1207</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="L2">
-        <v>1000000</v>
+      <c r="L2" s="9">
+        <v>10000000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D541D76-4C00-4D7E-846F-BB06E806247C}">
+          <x14:formula1>
+            <xm:f>'Unit Divisi'!$F$2:$F$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7DBBCD95-FF0B-4171-BD3C-66977EECE152}">
+          <x14:formula1>
+            <xm:f>'Unit Divisi'!$D$2:$D$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{558C1FFE-8BCF-475D-B708-F3F6925D405D}">
+          <x14:formula1>
+            <xm:f>'Unit Divisi'!$B$2:$B$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0B039B81-5133-42A8-84A3-0FC81C2891D2}">
+          <x14:formula1>
+            <xm:f>'Sumber Anggaran'!$A$1:$A$21</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C799652F-401C-463D-B8F9-ED5847C8958D}">
+          <x14:formula1>
+            <xm:f>'Daftar Kegiatan'!$D$1:$D$274</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1274383A-5CD7-4FDC-AB61-A406F7FAA676}">
+          <x14:formula1>
+            <xm:f>'Daftar Akun'!$D$1:$D$124</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:K1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -5529,7 +5677,7 @@
         <v>250</v>
       </c>
       <c r="D115" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -8780,4 +8928,126 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B481A195-EB99-46F2-A843-0B0B0A13C4D3}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>